--- a/CPRD Raw Analysis/Results/Output_yearly_costs_Raw.xlsx
+++ b/CPRD Raw Analysis/Results/Output_yearly_costs_Raw.xlsx
@@ -402,25 +402,25 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>510.67</v>
+        <v>643.72</v>
       </c>
       <c r="C2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D2">
-        <v>3650.26</v>
+        <v>9656.440000000001</v>
       </c>
       <c r="E2">
-        <v>479.4</v>
+        <v>543.55</v>
       </c>
       <c r="F2">
-        <v>370.78</v>
+        <v>504</v>
       </c>
       <c r="G2">
-        <v>168</v>
+        <v>282.69</v>
       </c>
       <c r="H2">
-        <v>692.35</v>
+        <v>840</v>
       </c>
     </row>
     <row r="3">
@@ -428,25 +428,25 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>593.58</v>
+        <v>276.39</v>
       </c>
       <c r="C3">
         <v>3</v>
       </c>
       <c r="D3">
-        <v>7049.25</v>
+        <v>3101.25</v>
       </c>
       <c r="E3">
-        <v>478.21</v>
+        <v>250.52</v>
       </c>
       <c r="F3">
-        <v>474.62</v>
+        <v>210</v>
       </c>
       <c r="G3">
-        <v>273</v>
+        <v>105</v>
       </c>
       <c r="H3">
-        <v>775.2</v>
+        <v>363.08</v>
       </c>
     </row>
   </sheetData>
@@ -506,25 +506,25 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>480.35</v>
+        <v>628.75</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>3650.26</v>
+        <v>9656.440000000001</v>
       </c>
       <c r="E2">
-        <v>480.36</v>
+        <v>545.88</v>
       </c>
       <c r="F2">
-        <v>336</v>
+        <v>504</v>
       </c>
       <c r="G2">
-        <v>126</v>
+        <v>252</v>
       </c>
       <c r="H2">
-        <v>672</v>
+        <v>840</v>
       </c>
     </row>
     <row r="3">
@@ -532,25 +532,25 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>589.03</v>
+        <v>268.04</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>7049.25</v>
+        <v>3101.25</v>
       </c>
       <c r="E3">
-        <v>479.18</v>
+        <v>251.2</v>
       </c>
       <c r="F3">
-        <v>471.6</v>
+        <v>206.39</v>
       </c>
       <c r="G3">
-        <v>273</v>
+        <v>105</v>
       </c>
       <c r="H3">
-        <v>769.37</v>
+        <v>357</v>
       </c>
     </row>
   </sheetData>

--- a/CPRD Raw Analysis/Results/Output_yearly_costs_Raw.xlsx
+++ b/CPRD Raw Analysis/Results/Output_yearly_costs_Raw.xlsx
@@ -402,25 +402,25 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>643.72</v>
+        <v>735.26</v>
       </c>
       <c r="C2">
         <v>6</v>
       </c>
       <c r="D2">
-        <v>9656.440000000001</v>
+        <v>9698.440000000001</v>
       </c>
       <c r="E2">
-        <v>543.55</v>
+        <v>647.39</v>
       </c>
       <c r="F2">
-        <v>504</v>
+        <v>560.22</v>
       </c>
       <c r="G2">
-        <v>282.69</v>
+        <v>313.2</v>
       </c>
       <c r="H2">
-        <v>840</v>
+        <v>943.73</v>
       </c>
     </row>
     <row r="3">
@@ -428,25 +428,25 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>276.39</v>
+        <v>597.5</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>6.01</v>
       </c>
       <c r="D3">
-        <v>3101.25</v>
+        <v>6546.96</v>
       </c>
       <c r="E3">
-        <v>250.52</v>
+        <v>559.46</v>
       </c>
       <c r="F3">
-        <v>210</v>
+        <v>446.84</v>
       </c>
       <c r="G3">
-        <v>105</v>
+        <v>229.51</v>
       </c>
       <c r="H3">
-        <v>363.08</v>
+        <v>778.51</v>
       </c>
     </row>
   </sheetData>
@@ -506,25 +506,25 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>628.75</v>
+        <v>718.23</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>9656.440000000001</v>
+        <v>9698.440000000001</v>
       </c>
       <c r="E2">
-        <v>545.88</v>
+        <v>649.34</v>
       </c>
       <c r="F2">
-        <v>504</v>
+        <v>546</v>
       </c>
       <c r="G2">
-        <v>252</v>
+        <v>294</v>
       </c>
       <c r="H2">
-        <v>840</v>
+        <v>925.41</v>
       </c>
     </row>
     <row r="3">
@@ -532,25 +532,25 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>268.04</v>
+        <v>579.49</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>3101.25</v>
+        <v>6546.96</v>
       </c>
       <c r="E3">
-        <v>251.2</v>
+        <v>560.36</v>
       </c>
       <c r="F3">
-        <v>206.39</v>
+        <v>420.58</v>
       </c>
       <c r="G3">
-        <v>105</v>
+        <v>210.29</v>
       </c>
       <c r="H3">
-        <v>357</v>
+        <v>757.04</v>
       </c>
     </row>
   </sheetData>

--- a/CPRD Raw Analysis/Results/Output_yearly_costs_Raw.xlsx
+++ b/CPRD Raw Analysis/Results/Output_yearly_costs_Raw.xlsx
@@ -402,25 +402,25 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>735.26</v>
+        <v>759.8</v>
       </c>
       <c r="C2">
         <v>6</v>
       </c>
       <c r="D2">
-        <v>9698.440000000001</v>
+        <v>9487.129999999999</v>
       </c>
       <c r="E2">
-        <v>647.39</v>
+        <v>691.03</v>
       </c>
       <c r="F2">
-        <v>560.22</v>
+        <v>564.55</v>
       </c>
       <c r="G2">
-        <v>313.2</v>
+        <v>309.02</v>
       </c>
       <c r="H2">
-        <v>943.73</v>
+        <v>972.23</v>
       </c>
     </row>
     <row r="3">
@@ -428,7 +428,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>597.5</v>
+        <v>587.72</v>
       </c>
       <c r="C3">
         <v>6.01</v>
@@ -437,16 +437,16 @@
         <v>6546.96</v>
       </c>
       <c r="E3">
-        <v>559.46</v>
+        <v>553.87</v>
       </c>
       <c r="F3">
-        <v>446.84</v>
+        <v>432.42</v>
       </c>
       <c r="G3">
-        <v>229.51</v>
+        <v>214.23</v>
       </c>
       <c r="H3">
-        <v>778.51</v>
+        <v>757.21</v>
       </c>
     </row>
   </sheetData>
@@ -506,25 +506,25 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>718.23</v>
+        <v>733.01</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>9698.440000000001</v>
+        <v>9487.129999999999</v>
       </c>
       <c r="E2">
-        <v>649.34</v>
+        <v>693.05</v>
       </c>
       <c r="F2">
         <v>546</v>
       </c>
       <c r="G2">
-        <v>294</v>
+        <v>292.19</v>
       </c>
       <c r="H2">
-        <v>925.41</v>
+        <v>958.78</v>
       </c>
     </row>
     <row r="3">
@@ -532,7 +532,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>579.49</v>
+        <v>568.7</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -541,7 +541,7 @@
         <v>6546.96</v>
       </c>
       <c r="E3">
-        <v>560.36</v>
+        <v>554.67</v>
       </c>
       <c r="F3">
         <v>420.58</v>
